--- a/DATA/Aggregated data/M2/M2 aggregated.xlsx
+++ b/DATA/Aggregated data/M2/M2 aggregated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Desktop\Masterproef\DATA\Aggregated data\M2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\GitHub\Masterthesis\DATA\Aggregated data\M2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FB0F86-5B35-4844-B5B4-4AE063BAD1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5C4DEA-C47A-4B9C-B6A7-E9AACBB56D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5050,7 +5050,7 @@
         <v>13962073368329.193</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="K5:M5" si="2">AVERAGE(E2:E130)</f>
+        <f t="shared" ref="L5:M5" si="2">AVERAGE(E2:E130)</f>
         <v>21844018627906.977</v>
       </c>
       <c r="M5">
